--- a/media/exports/黄胜原_8718_认定表.xlsx
+++ b/media/exports/黄胜原_8718_认定表.xlsx
@@ -938,10 +938,9 @@
       </c>
       <c r="B4" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">    黄胜原同志档案中最早形成的《入团志愿书》中记载的出生年月为：1986年1月，其档案中有记载1986年1月的情况。《大中专毕业学转正定级工资表》中记载的参加工作时间为：2004年12月，其档案中有记载为2004年12月的情况。2004年12月1日形成的《初聘专业技术职务呈报表》中有涂改的情况，涂改后参加工作时间为2004年12月。
-工工工工工工工工工a
-    根据《中共中央组织部、人事部、公安部关于认真做好干部出生日期管理工作的通知》（组通字〔2006〕41号）及中共中央组织部《组工通讯》第10期相关规定，经集体研究，综合研判，建议黄胜原同志出生年月按1986年1月进行认定。参加工作时间按2004年12月进行认定。
-</t>
+          <t xml:space="preserve">    黄胜原同志档案中最早形成的《入团志愿书》中记载的出生年月为：1986年1月,其档案中有记载1986年1月的情况。《大中专毕业学转正定级工资表》中记载的参加工作时间为：2004年12月,其档案中有记载为2004年12月的情况。2004年12月1日形成的《初聘专业技术职务呈报表》中有涂改的情况，涂改后参加工作时间为2004年12月。
+    根据《中共中央组织部、人事部、公安部关于认真做好干部出生日期管理工作的通知》（组通字〔2006〕
+41号）及中共中央组织部《组工通讯》第10期相关规定，建议黄胜原同志出生年月按1986年1月进行认定。参加工作时间按2004年12月进行认定。</t>
         </is>
       </c>
       <c r="C4" s="52" t="n"/>
@@ -1080,7 +1079,7 @@
       <c r="B24" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">
-    经综合研判，2016年3月1日，中共盘州市教育局党组会议研究，认定黄胜原同志出生年月为1986年1月，参加工作时间为2004年12月。</t>
+    经综合研判，[(dzhsj)格式有误，请手动修改！]，中共盘州市教育局党组会议研究，认定黄胜原同志出生年月为1986年1月,参加工作时间为2004年12月。</t>
         </is>
       </c>
       <c r="C24" s="52" t="n"/>
